--- a/Excel/Avg/Rata-rata-128.xlsx
+++ b/Excel/Avg/Rata-rata-128.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Avg\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266B68BC-3FCB-4271-A8B0-575C020EC353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Waktu Pencarian" sheetId="1" r:id="rId1"/>
@@ -20,18 +14,7 @@
     <sheet name="Jumlah Close" sheetId="5" r:id="rId5"/>
     <sheet name="Jumlah Belok" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -254,8 +237,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,1508 +301,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$A$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>A*</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Map 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Map 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Map 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Map 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Map 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$B$2:$F$2</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.197515</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13250819999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.110197</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.22436320000000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.34176450000000003</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AABB-4335-B310-A7D5495A2586}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$A$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BDS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Map 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Map 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Map 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Map 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Map 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$B$3:$F$3</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2.6299799999999991E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.2051600000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.7858200000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.1933899999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.6024400000000001E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-AABB-4335-B310-A7D5495A2586}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$A$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>BRC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Map 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Map 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Map 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Map 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Map 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$B$4:$F$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.1765678</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.18647659999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.6599900000000004E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.80442E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.3635400000000001E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-AABB-4335-B310-A7D5495A2586}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>GL</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Map 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Map 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Map 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Map 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Map 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$B$5:$F$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.17614659999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.1149251</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.9039199999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.1253619</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.16289010000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-AABB-4335-B310-A7D5495A2586}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$A$6</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>JPS</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent5"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Map 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Map 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Map 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Map 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Map 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$B$6:$F$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>2.86468E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.29208E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2.15891E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.0586199999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3.3102199999999998E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-AABB-4335-B310-A7D5495A2586}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>PPO</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Map 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Map 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Map 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Map 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Map 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$B$7:$F$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.19919429999999999</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13209070000000001</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.1104907</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.22379499999999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.34366750000000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-AABB-4335-B310-A7D5495A2586}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="6"/>
-          <c:order val="6"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TPF</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="60000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Waktu Pencarian'!$B$1:$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>Map 1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Map 2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Map 3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Map 4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Map 5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Waktu Pencarian'!$B$8:$F$8</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.19535810000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.12540699999999999</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.9208500000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.2119598</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.34526259999999998</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-AABB-4335-B310-A7D5495A2586}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1619155951"/>
-        <c:axId val="1619173711"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1619155951"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1619173711"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1619173711"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="id-ID"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1619155951"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="id-ID"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="id-ID"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>34290</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB622BAC-7DF9-657C-EE0B-BF704E76AAB5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1857,7 +345,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1891,7 +379,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1926,10 +413,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2102,11 +588,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2129,1490 +615,1489 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2">
-        <v>0.197515</v>
+        <v>0.2286019</v>
       </c>
       <c r="C2">
-        <v>0.13250819999999999</v>
+        <v>0.1528557</v>
       </c>
       <c r="D2">
-        <v>0.110197</v>
+        <v>0.1271498</v>
       </c>
       <c r="E2">
-        <v>0.22436320000000001</v>
+        <v>0.2616813</v>
       </c>
       <c r="F2">
-        <v>0.34176450000000003</v>
+        <v>0.3945116</v>
       </c>
       <c r="G2">
-        <v>0.20126958</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.23296006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>2.6299799999999991E-2</v>
+        <v>0.0306146</v>
       </c>
       <c r="C3">
-        <v>2.2051600000000001E-2</v>
+        <v>0.0254445</v>
       </c>
       <c r="D3">
-        <v>1.7858200000000001E-2</v>
+        <v>0.0205801</v>
       </c>
       <c r="E3">
-        <v>2.1933899999999999E-2</v>
+        <v>0.025287</v>
       </c>
       <c r="F3">
-        <v>1.6024400000000001E-2</v>
+        <v>0.0184169</v>
       </c>
       <c r="G3">
-        <v>2.0833580000000001E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02406862</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4">
-        <v>0.1765678</v>
+        <v>0.2061049</v>
       </c>
       <c r="C4">
-        <v>0.18647659999999999</v>
+        <v>0.2165962</v>
       </c>
       <c r="D4">
-        <v>6.6599900000000004E-2</v>
+        <v>0.07728009999999999</v>
       </c>
       <c r="E4">
-        <v>3.80442E-2</v>
+        <v>0.0442719</v>
       </c>
       <c r="F4">
-        <v>2.3635400000000001E-2</v>
+        <v>0.0273797</v>
       </c>
       <c r="G4">
-        <v>9.8264779999999982E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.11432656</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0.17614659999999999</v>
+        <v>0.2052934</v>
       </c>
       <c r="C5">
-        <v>0.1149251</v>
+        <v>0.1332297</v>
       </c>
       <c r="D5">
-        <v>8.9039199999999999E-2</v>
+        <v>0.1026107</v>
       </c>
       <c r="E5">
-        <v>0.1253619</v>
+        <v>0.1464506</v>
       </c>
       <c r="F5">
-        <v>0.16289010000000001</v>
+        <v>0.1876085</v>
       </c>
       <c r="G5">
-        <v>0.13367258000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.15503858</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6">
-        <v>2.86468E-2</v>
+        <v>0.033018</v>
       </c>
       <c r="C6">
-        <v>1.29208E-2</v>
+        <v>0.015033</v>
       </c>
       <c r="D6">
-        <v>2.15891E-2</v>
+        <v>0.0249368</v>
       </c>
       <c r="E6">
-        <v>2.0586199999999999E-2</v>
+        <v>0.0238697</v>
       </c>
       <c r="F6">
-        <v>3.3102199999999998E-2</v>
+        <v>0.0382735</v>
       </c>
       <c r="G6">
-        <v>2.3369020000000001E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0270262</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0.19919429999999999</v>
+        <v>0.2315717</v>
       </c>
       <c r="C7">
-        <v>0.13209070000000001</v>
+        <v>0.1524983</v>
       </c>
       <c r="D7">
-        <v>0.1104907</v>
+        <v>0.1282538</v>
       </c>
       <c r="E7">
-        <v>0.22379499999999999</v>
+        <v>0.259291</v>
       </c>
       <c r="F7">
-        <v>0.34366750000000001</v>
+        <v>0.3975153</v>
       </c>
       <c r="G7">
-        <v>0.20184763999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.23382602</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8">
-        <v>0.19535810000000001</v>
+        <v>0.2254631</v>
       </c>
       <c r="C8">
-        <v>0.12540699999999999</v>
+        <v>0.1442962</v>
       </c>
       <c r="D8">
-        <v>9.9208500000000005E-2</v>
+        <v>0.1141287</v>
       </c>
       <c r="E8">
-        <v>0.2119598</v>
+        <v>0.2454593</v>
       </c>
       <c r="F8">
-        <v>0.34526259999999998</v>
+        <v>0.3935329</v>
       </c>
       <c r="G8">
-        <v>0.19543920000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.22457604</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9">
-        <v>5.3467999999999988E-2</v>
+        <v>0.062343</v>
       </c>
       <c r="C9">
-        <v>5.5286200000000008E-2</v>
+        <v>0.0635578</v>
       </c>
       <c r="D9">
-        <v>2.1674600000000009E-2</v>
+        <v>0.0250588</v>
       </c>
       <c r="E9">
-        <v>1.26698E-2</v>
+        <v>0.0145066</v>
       </c>
       <c r="F9">
-        <v>7.6482000000000008E-3</v>
+        <v>0.009182899999999999</v>
       </c>
       <c r="G9">
-        <v>3.014936E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03492982</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10">
-        <v>3.08908E-2</v>
+        <v>0.0355479</v>
       </c>
       <c r="C10">
-        <v>2.61967E-2</v>
+        <v>0.0303686</v>
       </c>
       <c r="D10">
-        <v>1.7460300000000002E-2</v>
+        <v>0.0201795</v>
       </c>
       <c r="E10">
-        <v>2.6906599999999999E-2</v>
+        <v>0.0313341</v>
       </c>
       <c r="F10">
-        <v>2.20319E-2</v>
+        <v>0.0255828</v>
       </c>
       <c r="G10">
-        <v>2.4697259999999999E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02860258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11">
-        <v>2.7446100000000001E-2</v>
+        <v>0.0315156</v>
       </c>
       <c r="C11">
-        <v>2.30846E-2</v>
+        <v>0.0265525</v>
       </c>
       <c r="D11">
-        <v>1.8587599999999999E-2</v>
+        <v>0.021235</v>
       </c>
       <c r="E11">
-        <v>2.2897299999999999E-2</v>
+        <v>0.0262043</v>
       </c>
       <c r="F11">
-        <v>1.7125999999999999E-2</v>
+        <v>0.0194662</v>
       </c>
       <c r="G11">
-        <v>2.1828319999999998E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02499472</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
-        <v>2.78505E-2</v>
+        <v>0.0328049</v>
       </c>
       <c r="C12">
-        <v>2.2777499999999999E-2</v>
+        <v>0.0269336</v>
       </c>
       <c r="D12">
-        <v>1.8370899999999999E-2</v>
+        <v>0.0215146</v>
       </c>
       <c r="E12">
-        <v>2.2790299999999999E-2</v>
+        <v>0.0268435</v>
       </c>
       <c r="F12">
-        <v>1.6440799999999998E-2</v>
+        <v>0.019238</v>
       </c>
       <c r="G12">
-        <v>2.1645999999999999E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02546692</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.17783640000000001</v>
+        <v>0.206583</v>
       </c>
       <c r="C13">
-        <v>0.188642</v>
+        <v>0.2171667</v>
       </c>
       <c r="D13">
-        <v>6.7339100000000013E-2</v>
+        <v>0.0778155</v>
       </c>
       <c r="E13">
-        <v>3.9035199999999992E-2</v>
+        <v>0.0449362</v>
       </c>
       <c r="F13">
-        <v>2.4821599999999999E-2</v>
+        <v>0.028692</v>
       </c>
       <c r="G13">
-        <v>9.9534859999999989E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.11503868</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.19455410000000001</v>
+        <v>0.2289547</v>
       </c>
       <c r="C14">
-        <v>0.17534749999999999</v>
+        <v>0.2050854</v>
       </c>
       <c r="D14">
-        <v>9.5681599999999992E-2</v>
+        <v>0.1106708</v>
       </c>
       <c r="E14">
-        <v>3.2273800000000012E-2</v>
+        <v>0.0379847</v>
       </c>
       <c r="F14">
-        <v>2.2407300000000002E-2</v>
+        <v>0.0263261</v>
       </c>
       <c r="G14">
-        <v>0.10405286</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.12180434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.22276109999999999</v>
+        <v>0.2606994</v>
       </c>
       <c r="C15">
-        <v>0.22212699999999999</v>
+        <v>0.2590863</v>
       </c>
       <c r="D15">
-        <v>6.7815099999999989E-2</v>
+        <v>0.07777999999999999</v>
       </c>
       <c r="E15">
-        <v>3.1568499999999999E-2</v>
+        <v>0.0366691</v>
       </c>
       <c r="F15">
-        <v>6.75756E-2</v>
+        <v>0.0775763</v>
       </c>
       <c r="G15">
-        <v>0.12236946</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.14236222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.1774308</v>
+        <v>0.2069834</v>
       </c>
       <c r="C16">
-        <v>0.1159927</v>
+        <v>0.1351473</v>
       </c>
       <c r="D16">
-        <v>9.0079700000000013E-2</v>
+        <v>0.1051822</v>
       </c>
       <c r="E16">
-        <v>0.1260309</v>
+        <v>0.1472262</v>
       </c>
       <c r="F16">
-        <v>0.16406950000000001</v>
+        <v>0.19031</v>
       </c>
       <c r="G16">
-        <v>0.13472071999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.15696982</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17">
-        <v>0.16531850000000001</v>
+        <v>0.1918347</v>
       </c>
       <c r="C17">
-        <v>0.1112421</v>
+        <v>0.1294604</v>
       </c>
       <c r="D17">
-        <v>8.4493900000000011E-2</v>
+        <v>0.0970391</v>
       </c>
       <c r="E17">
-        <v>0.11432489999999999</v>
+        <v>0.1334328</v>
       </c>
       <c r="F17">
-        <v>0.15543570000000001</v>
+        <v>0.1771327</v>
       </c>
       <c r="G17">
-        <v>0.12616301999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.14577994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18">
-        <v>1.64178E-2</v>
+        <v>0.0190694</v>
       </c>
       <c r="C18">
-        <v>1.14609E-2</v>
+        <v>0.0132407</v>
       </c>
       <c r="D18">
-        <v>1.60094E-2</v>
+        <v>0.0187438</v>
       </c>
       <c r="E18">
-        <v>1.07975E-2</v>
+        <v>0.012631</v>
       </c>
       <c r="F18">
-        <v>2.3695500000000001E-2</v>
+        <v>0.0275139</v>
       </c>
       <c r="G18">
-        <v>1.5676220000000001E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01823976</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19">
-        <v>1.49537E-2</v>
+        <v>0.0172391</v>
       </c>
       <c r="C19">
-        <v>1.24311E-2</v>
+        <v>0.0144885</v>
       </c>
       <c r="D19">
-        <v>7.7940000000000006E-3</v>
+        <v>0.0090408</v>
       </c>
       <c r="E19">
-        <v>8.9954000000000006E-3</v>
+        <v>0.0104552</v>
       </c>
       <c r="F19">
-        <v>1.6797699999999999E-2</v>
+        <v>0.0190797</v>
       </c>
       <c r="G19">
-        <v>1.2194379999999999E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01406066</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>25</v>
       </c>
       <c r="B20">
-        <v>2.2743099999999999E-2</v>
+        <v>0.02640940000000001</v>
       </c>
       <c r="C20">
-        <v>1.40915E-2</v>
+        <v>0.0162659</v>
       </c>
       <c r="D20">
-        <v>1.46006E-2</v>
+        <v>0.0169771</v>
       </c>
       <c r="E20">
-        <v>1.47949E-2</v>
+        <v>0.0172664</v>
       </c>
       <c r="F20">
-        <v>2.51948E-2</v>
+        <v>0.0292527</v>
       </c>
       <c r="G20">
-        <v>1.8284979999999999E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0212343</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>26</v>
       </c>
       <c r="B21">
-        <v>2.8681700000000001E-2</v>
+        <v>0.03309700000000001</v>
       </c>
       <c r="C21">
-        <v>1.2908899999999999E-2</v>
+        <v>0.0150827</v>
       </c>
       <c r="D21">
-        <v>2.16055E-2</v>
+        <v>0.0250355</v>
       </c>
       <c r="E21">
-        <v>2.0831499999999999E-2</v>
+        <v>0.0240392</v>
       </c>
       <c r="F21">
-        <v>3.3197900000000002E-2</v>
+        <v>0.03865449999999999</v>
       </c>
       <c r="G21">
-        <v>2.34451E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02718178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22">
-        <v>3.1123000000000001E-2</v>
+        <v>0.033023</v>
       </c>
       <c r="C22">
-        <v>1.14371E-2</v>
+        <v>0.0149186</v>
       </c>
       <c r="D22">
-        <v>2.04785E-2</v>
+        <v>0.0249886</v>
       </c>
       <c r="E22">
-        <v>1.8698900000000001E-2</v>
+        <v>0.02397</v>
       </c>
       <c r="F22">
-        <v>3.2010600000000007E-2</v>
+        <v>0.0385824</v>
       </c>
       <c r="G22">
-        <v>2.2749620000000009E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02709652</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0.19544700000000001</v>
+        <v>0.2243565</v>
       </c>
       <c r="C23">
-        <v>0.1267848</v>
+        <v>0.1450691</v>
       </c>
       <c r="D23">
-        <v>9.9814399999999998E-2</v>
+        <v>0.1149933</v>
       </c>
       <c r="E23">
-        <v>0.2121102</v>
+        <v>0.2461289</v>
       </c>
       <c r="F23">
-        <v>0.34593869999999999</v>
+        <v>0.3938963</v>
       </c>
       <c r="G23">
-        <v>0.19601901999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.22488882</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24">
-        <v>5.46624E-2</v>
+        <v>0.06348390000000001</v>
       </c>
       <c r="C24">
-        <v>5.62427E-2</v>
+        <v>0.06475070000000001</v>
       </c>
       <c r="D24">
-        <v>2.2144799999999999E-2</v>
+        <v>0.02573880000000001</v>
       </c>
       <c r="E24">
-        <v>1.3449300000000001E-2</v>
+        <v>0.0153717</v>
       </c>
       <c r="F24">
-        <v>8.5313999999999997E-3</v>
+        <v>0.0100427</v>
       </c>
       <c r="G24">
-        <v>3.1006120000000002E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03587756</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25">
-        <v>5.3803999999999998E-2</v>
+        <v>0.063337</v>
       </c>
       <c r="C25">
-        <v>5.6122699999999998E-2</v>
+        <v>0.06587010000000001</v>
       </c>
       <c r="D25">
-        <v>2.8437899999999999E-2</v>
+        <v>0.0330973</v>
       </c>
       <c r="E25">
-        <v>1.3686200000000001E-2</v>
+        <v>0.015544</v>
       </c>
       <c r="F25">
-        <v>7.4463000000000003E-3</v>
+        <v>0.008756299999999998</v>
       </c>
       <c r="G25">
-        <v>3.1899419999999998E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03732094</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>31</v>
       </c>
       <c r="B26">
-        <v>5.8112700000000003E-2</v>
+        <v>0.067452</v>
       </c>
       <c r="C26">
-        <v>9.2565999999999996E-2</v>
+        <v>0.107224</v>
       </c>
       <c r="D26">
-        <v>3.8056199999999998E-2</v>
+        <v>0.04386379999999999</v>
       </c>
       <c r="E26">
-        <v>1.5634800000000001E-2</v>
+        <v>0.0181513</v>
       </c>
       <c r="F26">
-        <v>3.4495199999999997E-2</v>
+        <v>0.0403214</v>
       </c>
       <c r="G26">
-        <v>4.777298E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0554025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>32</v>
       </c>
       <c r="B27">
-        <v>3.1600299999999998E-2</v>
+        <v>0.0366261</v>
       </c>
       <c r="C27">
-        <v>2.7212699999999999E-2</v>
+        <v>0.0312755</v>
       </c>
       <c r="D27">
-        <v>1.8183899999999999E-2</v>
+        <v>0.0209344</v>
       </c>
       <c r="E27">
-        <v>2.77541E-2</v>
+        <v>0.031981</v>
       </c>
       <c r="F27">
-        <v>2.3395900000000001E-2</v>
+        <v>0.0266014</v>
       </c>
       <c r="G27">
-        <v>2.562938E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02948368</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="B28">
-        <v>3.1383399999999999E-2</v>
+        <v>0.0371171</v>
       </c>
       <c r="C28">
-        <v>2.7155499999999999E-2</v>
+        <v>0.03220050000000001</v>
       </c>
       <c r="D28">
-        <v>1.7717199999999999E-2</v>
+        <v>0.0208596</v>
       </c>
       <c r="E28">
-        <v>2.6405600000000001E-2</v>
+        <v>0.0309528</v>
       </c>
       <c r="F28">
-        <v>2.2834799999999999E-2</v>
+        <v>0.0271826</v>
       </c>
       <c r="G28">
-        <v>2.5099300000000001E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02966252</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29">
-        <v>2.8932300000000001E-2</v>
+        <v>0.03387150000000001</v>
       </c>
       <c r="C29">
-        <v>2.3904999999999999E-2</v>
+        <v>0.0279524</v>
       </c>
       <c r="D29">
-        <v>1.9021E-2</v>
+        <v>0.0222006</v>
       </c>
       <c r="E29">
-        <v>2.3451099999999999E-2</v>
+        <v>0.0274426</v>
       </c>
       <c r="F29">
-        <v>1.7524000000000001E-2</v>
+        <v>0.0203046</v>
       </c>
       <c r="G29">
-        <v>2.2566679999999999E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02635434</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30">
-        <v>0.19603880000000001</v>
+        <v>0.2292595</v>
       </c>
       <c r="C30">
-        <v>0.1762128</v>
+        <v>0.2061472</v>
       </c>
       <c r="D30">
-        <v>9.6409800000000004E-2</v>
+        <v>0.1119938</v>
       </c>
       <c r="E30">
-        <v>3.2882300000000003E-2</v>
+        <v>0.0388375</v>
       </c>
       <c r="F30">
-        <v>2.3720700000000001E-2</v>
+        <v>0.0277705</v>
       </c>
       <c r="G30">
-        <v>0.10505288</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1228017</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="B31">
-        <v>0.2236168</v>
+        <v>0.2595298</v>
       </c>
       <c r="C31">
-        <v>0.2224198</v>
+        <v>0.2602249</v>
       </c>
       <c r="D31">
-        <v>6.8105900000000011E-2</v>
+        <v>0.07864350000000001</v>
       </c>
       <c r="E31">
-        <v>3.2521500000000002E-2</v>
+        <v>0.03758400000000001</v>
       </c>
       <c r="F31">
-        <v>6.8606999999999987E-2</v>
+        <v>0.0792209</v>
       </c>
       <c r="G31">
-        <v>0.1230542</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.14304062</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32">
-        <v>0.21637680000000001</v>
+        <v>0.2518425000000001</v>
       </c>
       <c r="C32">
-        <v>0.21738499999999999</v>
+        <v>0.2557045999999999</v>
       </c>
       <c r="D32">
-        <v>6.8396299999999993E-2</v>
+        <v>0.0802723</v>
       </c>
       <c r="E32">
-        <v>3.0172500000000001E-2</v>
+        <v>0.03526600000000001</v>
       </c>
       <c r="F32">
-        <v>6.0961500000000002E-2</v>
+        <v>0.0713316</v>
       </c>
       <c r="G32">
-        <v>0.11865842</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.1388834</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33">
-        <v>0.16626550000000001</v>
+        <v>0.1940657</v>
       </c>
       <c r="C33">
-        <v>0.11227330000000001</v>
+        <v>0.1301035</v>
       </c>
       <c r="D33">
-        <v>8.48579E-2</v>
+        <v>0.09824600000000001</v>
       </c>
       <c r="E33">
-        <v>0.1149911</v>
+        <v>0.1343485</v>
       </c>
       <c r="F33">
-        <v>0.15463250000000001</v>
+        <v>0.1768284</v>
       </c>
       <c r="G33">
-        <v>0.12660405999999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.14671842</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>39</v>
       </c>
       <c r="B34">
-        <v>1.36457E-2</v>
+        <v>0.0159775</v>
       </c>
       <c r="C34">
-        <v>1.2142E-2</v>
+        <v>0.0140503</v>
       </c>
       <c r="D34">
-        <v>9.6824000000000007E-3</v>
+        <v>0.0114112</v>
       </c>
       <c r="E34">
-        <v>1.2399E-2</v>
+        <v>0.0143498</v>
       </c>
       <c r="F34">
-        <v>2.53361E-2</v>
+        <v>0.0294727</v>
       </c>
       <c r="G34">
-        <v>1.4641039999999999E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0170523</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="B35">
-        <v>1.06531E-2</v>
+        <v>0.0124671</v>
       </c>
       <c r="C35">
-        <v>1.1829900000000001E-2</v>
+        <v>0.0136697</v>
       </c>
       <c r="D35">
-        <v>1.0708000000000001E-2</v>
+        <v>0.0124629</v>
       </c>
       <c r="E35">
-        <v>1.1266200000000001E-2</v>
+        <v>0.0131195</v>
       </c>
       <c r="F35">
-        <v>2.80714E-2</v>
+        <v>0.03256189999999999</v>
       </c>
       <c r="G35">
-        <v>1.450572E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01685622</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>41</v>
       </c>
       <c r="B36">
-        <v>1.66801E-2</v>
+        <v>0.0192145</v>
       </c>
       <c r="C36">
-        <v>1.1647299999999999E-2</v>
+        <v>0.0134025</v>
       </c>
       <c r="D36">
-        <v>1.6158499999999999E-2</v>
+        <v>0.0187536</v>
       </c>
       <c r="E36">
-        <v>1.0868600000000001E-2</v>
+        <v>0.0126534</v>
       </c>
       <c r="F36">
-        <v>2.3981599999999999E-2</v>
+        <v>0.0276812</v>
       </c>
       <c r="G36">
-        <v>1.5867220000000001E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01834104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37">
-        <v>1.8203E-2</v>
+        <v>0.0192009</v>
       </c>
       <c r="C37">
-        <v>2.0368799999999999E-2</v>
+        <v>0.0132806</v>
       </c>
       <c r="D37">
-        <v>1.38598E-2</v>
+        <v>0.0186764</v>
       </c>
       <c r="E37">
-        <v>2.1079500000000001E-2</v>
+        <v>0.0131588</v>
       </c>
       <c r="F37">
-        <v>2.05785E-2</v>
+        <v>0.0276123</v>
       </c>
       <c r="G37">
-        <v>1.8817919999999998E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0183858</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>43</v>
       </c>
       <c r="B38">
-        <v>1.5044699999999999E-2</v>
+        <v>0.0174732</v>
       </c>
       <c r="C38">
-        <v>1.25874E-2</v>
+        <v>0.0146192</v>
       </c>
       <c r="D38">
-        <v>7.9218000000000014E-3</v>
+        <v>0.009122</v>
       </c>
       <c r="E38">
-        <v>9.1440999999999988E-3</v>
+        <v>0.0106414</v>
       </c>
       <c r="F38">
-        <v>1.69044E-2</v>
+        <v>0.0191367</v>
       </c>
       <c r="G38">
-        <v>1.232048E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0141985</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39">
-        <v>1.27733E-2</v>
+        <v>0.0172726</v>
       </c>
       <c r="C39">
-        <v>1.2488300000000001E-2</v>
+        <v>0.0145674</v>
       </c>
       <c r="D39">
-        <v>7.7637000000000001E-3</v>
+        <v>0.009008199999999997</v>
       </c>
       <c r="E39">
-        <v>9.0197000000000003E-3</v>
+        <v>0.010471</v>
       </c>
       <c r="F39">
-        <v>1.6420299999999999E-2</v>
+        <v>0.0190675</v>
       </c>
       <c r="G39">
-        <v>1.169306E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01407734</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>45</v>
       </c>
       <c r="B40">
-        <v>1.64645E-2</v>
+        <v>0.0190965</v>
       </c>
       <c r="C40">
-        <v>1.3277199999999999E-2</v>
+        <v>0.0154869</v>
       </c>
       <c r="D40">
-        <v>1.04215E-2</v>
+        <v>0.0123009</v>
       </c>
       <c r="E40">
-        <v>8.5757999999999997E-3</v>
+        <v>0.0101474</v>
       </c>
       <c r="F40">
-        <v>1.41542E-2</v>
+        <v>0.0164974</v>
       </c>
       <c r="G40">
-        <v>1.257864E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01470582</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>46</v>
       </c>
       <c r="B41">
-        <v>2.2877999999999999E-2</v>
+        <v>0.0266861</v>
       </c>
       <c r="C41">
-        <v>1.4215E-2</v>
+        <v>0.0163852</v>
       </c>
       <c r="D41">
-        <v>1.4741000000000001E-2</v>
+        <v>0.0171331</v>
       </c>
       <c r="E41">
-        <v>1.5023399999999999E-2</v>
+        <v>0.0174503</v>
       </c>
       <c r="F41">
-        <v>2.5390699999999999E-2</v>
+        <v>0.0292971</v>
       </c>
       <c r="G41">
-        <v>1.844962E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02139036</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42">
-        <v>2.1428900000000001E-2</v>
+        <v>0.026422</v>
       </c>
       <c r="C42">
-        <v>1.40857E-2</v>
+        <v>0.0162808</v>
       </c>
       <c r="D42">
-        <v>1.5070200000000001E-2</v>
+        <v>0.0171107</v>
       </c>
       <c r="E42">
-        <v>1.4000500000000001E-2</v>
+        <v>0.0166392</v>
       </c>
       <c r="F42">
-        <v>2.8890699999999998E-2</v>
+        <v>0.0292396</v>
       </c>
       <c r="G42">
-        <v>1.8695199999999999E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02113846</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43">
-        <v>3.1252000000000002E-2</v>
+        <v>0.0332743</v>
       </c>
       <c r="C43">
-        <v>1.14999E-2</v>
+        <v>0.0149684</v>
       </c>
       <c r="D43">
-        <v>2.0591399999999999E-2</v>
+        <v>0.0250709</v>
       </c>
       <c r="E43">
-        <v>1.8775300000000002E-2</v>
+        <v>0.0252282</v>
       </c>
       <c r="F43">
-        <v>3.1999100000000003E-2</v>
+        <v>0.0383365</v>
       </c>
       <c r="G43">
-        <v>2.282354E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02737566</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44">
-        <v>5.5098599999999998E-2</v>
+        <v>0.0643161</v>
       </c>
       <c r="C44">
-        <v>5.6657100000000002E-2</v>
+        <v>0.06680419999999999</v>
       </c>
       <c r="D44">
-        <v>2.9291999999999999E-2</v>
+        <v>0.03383129999999999</v>
       </c>
       <c r="E44">
-        <v>1.4410299999999999E-2</v>
+        <v>0.016318</v>
       </c>
       <c r="F44">
-        <v>8.3744999999999983E-3</v>
+        <v>0.0097076</v>
       </c>
       <c r="G44">
-        <v>3.2766499999999997E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03819544</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>50</v>
       </c>
       <c r="B45">
-        <v>5.8895700000000002E-2</v>
+        <v>0.0680188</v>
       </c>
       <c r="C45">
-        <v>9.3612399999999998E-2</v>
+        <v>0.1084876</v>
       </c>
       <c r="D45">
-        <v>3.8730199999999999E-2</v>
+        <v>0.0446991</v>
       </c>
       <c r="E45">
-        <v>1.6479899999999999E-2</v>
+        <v>0.019092</v>
       </c>
       <c r="F45">
-        <v>3.6168899999999997E-2</v>
+        <v>0.0417714</v>
       </c>
       <c r="G45">
-        <v>4.8777420000000002E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.05641378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46">
-        <v>5.5644300000000001E-2</v>
+        <v>0.0662066</v>
       </c>
       <c r="C46">
-        <v>8.9513700000000002E-2</v>
+        <v>0.1076926</v>
       </c>
       <c r="D46">
-        <v>3.5798000000000003E-2</v>
+        <v>0.0422452</v>
       </c>
       <c r="E46">
-        <v>1.5300599999999999E-2</v>
+        <v>0.0179815</v>
       </c>
       <c r="F46">
-        <v>3.1302900000000002E-2</v>
+        <v>0.0368925</v>
       </c>
       <c r="G46">
-        <v>4.5511900000000001E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.05420368000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>52</v>
       </c>
       <c r="B47">
-        <v>3.2503299999999999E-2</v>
+        <v>0.0380678</v>
       </c>
       <c r="C47">
-        <v>2.8136100000000001E-2</v>
+        <v>0.0329255</v>
       </c>
       <c r="D47">
-        <v>1.84484E-2</v>
+        <v>0.0216426</v>
       </c>
       <c r="E47">
-        <v>2.72774E-2</v>
+        <v>0.0318849</v>
       </c>
       <c r="F47">
-        <v>2.4011000000000001E-2</v>
+        <v>0.02769310000000001</v>
       </c>
       <c r="G47">
-        <v>2.607524E-2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.03044278</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="B48">
-        <v>0.21788379999999999</v>
+        <v>0.2541017999999999</v>
       </c>
       <c r="C48">
-        <v>0.2182151</v>
+        <v>0.2570355</v>
       </c>
       <c r="D48">
-        <v>6.9092300000000009E-2</v>
+        <v>0.0809906</v>
       </c>
       <c r="E48">
-        <v>3.09024E-2</v>
+        <v>0.0358474</v>
       </c>
       <c r="F48">
-        <v>6.1866999999999991E-2</v>
+        <v>0.0729247</v>
       </c>
       <c r="G48">
-        <v>0.11959212</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.14018</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>54</v>
       </c>
       <c r="B49">
-        <v>1.38525E-2</v>
+        <v>0.0160479</v>
       </c>
       <c r="C49">
-        <v>1.22171E-2</v>
+        <v>0.0141368</v>
       </c>
       <c r="D49">
-        <v>9.8364999999999998E-3</v>
+        <v>0.011461</v>
       </c>
       <c r="E49">
-        <v>1.2658000000000001E-2</v>
+        <v>0.0144759</v>
       </c>
       <c r="F49">
-        <v>2.56043E-2</v>
+        <v>0.0296878</v>
       </c>
       <c r="G49">
-        <v>1.483368E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01716188</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="B50">
-        <v>1.5088499999999999E-2</v>
+        <v>0.0159904</v>
       </c>
       <c r="C50">
-        <v>1.4344900000000001E-2</v>
+        <v>0.0140877</v>
       </c>
       <c r="D50">
-        <v>1.1638300000000001E-2</v>
+        <v>0.0108684</v>
       </c>
       <c r="E50">
-        <v>1.5524400000000001E-2</v>
+        <v>0.0146131</v>
       </c>
       <c r="F50">
-        <v>2.0764299999999999E-2</v>
+        <v>0.0295836</v>
       </c>
       <c r="G50">
-        <v>1.5472079999999999E-2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01702864</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>56</v>
       </c>
       <c r="B51">
-        <v>1.0750900000000001E-2</v>
+        <v>0.0124926</v>
       </c>
       <c r="C51">
-        <v>1.32088E-2</v>
+        <v>0.0152476</v>
       </c>
       <c r="D51">
-        <v>1.1533399999999999E-2</v>
+        <v>0.0134001</v>
       </c>
       <c r="E51">
-        <v>1.1509500000000001E-2</v>
+        <v>0.0134396</v>
       </c>
       <c r="F51">
-        <v>2.6333599999999999E-2</v>
+        <v>0.0303552</v>
       </c>
       <c r="G51">
-        <v>1.466724E-2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01698702</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>57</v>
       </c>
       <c r="B52">
-        <v>1.08284E-2</v>
+        <v>0.0125327</v>
       </c>
       <c r="C52">
-        <v>1.19883E-2</v>
+        <v>0.0139248</v>
       </c>
       <c r="D52">
-        <v>1.0836699999999999E-2</v>
+        <v>0.0125483</v>
       </c>
       <c r="E52">
-        <v>1.14287E-2</v>
+        <v>0.0132008</v>
       </c>
       <c r="F52">
-        <v>2.8325199999999998E-2</v>
+        <v>0.03273690000000001</v>
       </c>
       <c r="G52">
-        <v>1.468146E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0169887</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>58</v>
       </c>
       <c r="B53">
-        <v>1.8557899999999999E-2</v>
+        <v>0.0130763</v>
       </c>
       <c r="C53">
-        <v>2.0159E-2</v>
+        <v>0.0138214</v>
       </c>
       <c r="D53">
-        <v>1.7440500000000001E-2</v>
+        <v>0.0125048</v>
       </c>
       <c r="E53">
-        <v>1.4369699999999999E-2</v>
+        <v>0.013144</v>
       </c>
       <c r="F53">
-        <v>2.0551E-2</v>
+        <v>0.0326732</v>
       </c>
       <c r="G53">
-        <v>1.8215619999999998E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01704394</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="B54">
-        <v>1.8351800000000001E-2</v>
+        <v>0.0192634</v>
       </c>
       <c r="C54">
-        <v>2.0473600000000002E-2</v>
+        <v>0.0134674</v>
       </c>
       <c r="D54">
-        <v>1.40676E-2</v>
+        <v>0.0188588</v>
       </c>
       <c r="E54">
-        <v>2.1375100000000001E-2</v>
+        <v>0.0131241</v>
       </c>
       <c r="F54">
-        <v>2.0987800000000001E-2</v>
+        <v>0.0276368</v>
       </c>
       <c r="G54">
-        <v>1.9051180000000001E-2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0184701</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>60</v>
       </c>
       <c r="B55">
-        <v>1.29379E-2</v>
+        <v>0.0174596</v>
       </c>
       <c r="C55">
-        <v>1.264E-2</v>
+        <v>0.0146179</v>
       </c>
       <c r="D55">
-        <v>7.8890000000000019E-3</v>
+        <v>0.009106699999999999</v>
       </c>
       <c r="E55">
-        <v>9.1442999999999993E-3</v>
+        <v>0.0106859</v>
       </c>
       <c r="F55">
-        <v>1.6578699999999998E-2</v>
+        <v>0.0191571</v>
       </c>
       <c r="G55">
-        <v>1.183798E-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01420544</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>61</v>
       </c>
       <c r="B56">
-        <v>1.66175E-2</v>
+        <v>0.0191897</v>
       </c>
       <c r="C56">
-        <v>1.35152E-2</v>
+        <v>0.0154912</v>
       </c>
       <c r="D56">
-        <v>1.06295E-2</v>
+        <v>0.0122903</v>
       </c>
       <c r="E56">
-        <v>8.7115999999999982E-3</v>
+        <v>0.0103104</v>
       </c>
       <c r="F56">
-        <v>1.42977E-2</v>
+        <v>0.0165873</v>
       </c>
       <c r="G56">
-        <v>1.27543E-2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01477378</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>62</v>
       </c>
       <c r="B57">
-        <v>1.6454799999999999E-2</v>
+        <v>0.0191566</v>
       </c>
       <c r="C57">
-        <v>1.3322000000000001E-2</v>
+        <v>0.0153767</v>
       </c>
       <c r="D57">
-        <v>1.0485299999999999E-2</v>
+        <v>0.0122923</v>
       </c>
       <c r="E57">
-        <v>8.5608999999999998E-3</v>
+        <v>0.0101752</v>
       </c>
       <c r="F57">
-        <v>1.4150100000000001E-2</v>
+        <v>0.0164473</v>
       </c>
       <c r="G57">
-        <v>1.2594620000000001E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01468962</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="B58">
-        <v>2.1530199999999999E-2</v>
+        <v>0.0265569</v>
       </c>
       <c r="C58">
-        <v>1.4293200000000001E-2</v>
+        <v>0.0164575</v>
       </c>
       <c r="D58">
-        <v>1.5196100000000001E-2</v>
+        <v>0.0171771</v>
       </c>
       <c r="E58">
-        <v>1.4165499999999999E-2</v>
+        <v>0.0167718</v>
       </c>
       <c r="F58">
-        <v>2.90803E-2</v>
+        <v>0.02937</v>
       </c>
       <c r="G58">
-        <v>1.8853060000000001E-2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.02126666</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>64</v>
       </c>
       <c r="B59">
-        <v>5.6629299999999987E-2</v>
+        <v>0.06688520000000001</v>
       </c>
       <c r="C59">
-        <v>9.0982299999999988E-2</v>
+        <v>0.1091924</v>
       </c>
       <c r="D59">
-        <v>3.6214700000000002E-2</v>
+        <v>0.0428622</v>
       </c>
       <c r="E59">
-        <v>1.6293800000000001E-2</v>
+        <v>0.0189664</v>
       </c>
       <c r="F59">
-        <v>3.2624100000000003E-2</v>
+        <v>0.0382842</v>
       </c>
       <c r="G59">
-        <v>4.6548840000000001E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.05523808</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>65</v>
       </c>
       <c r="B60">
-        <v>1.5263000000000001E-2</v>
+        <v>0.0160647</v>
       </c>
       <c r="C60">
-        <v>1.4567699999999999E-2</v>
+        <v>0.0141561</v>
       </c>
       <c r="D60">
-        <v>1.17286E-2</v>
+        <v>0.0110325</v>
       </c>
       <c r="E60">
-        <v>1.5631200000000001E-2</v>
+        <v>0.0145127</v>
       </c>
       <c r="F60">
-        <v>2.10032E-2</v>
+        <v>0.0297245</v>
       </c>
       <c r="G60">
-        <v>1.5638740000000002E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.0170981</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>66</v>
       </c>
       <c r="B61">
-        <v>1.09078E-2</v>
+        <v>0.0126608</v>
       </c>
       <c r="C61">
-        <v>1.3374199999999999E-2</v>
+        <v>0.0154642</v>
       </c>
       <c r="D61">
-        <v>1.1731699999999999E-2</v>
+        <v>0.0135899</v>
       </c>
       <c r="E61">
-        <v>1.17327E-2</v>
+        <v>0.0135151</v>
       </c>
       <c r="F61">
-        <v>2.6471399999999999E-2</v>
+        <v>0.0306753</v>
       </c>
       <c r="G61">
-        <v>1.484356E-2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01718106</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="B62">
-        <v>1.72666E-2</v>
+        <v>0.012526</v>
       </c>
       <c r="C62">
-        <v>1.4032299999999999E-2</v>
+        <v>0.0153321</v>
       </c>
       <c r="D62">
-        <v>1.7866300000000002E-2</v>
+        <v>0.0134724</v>
       </c>
       <c r="E62">
-        <v>1.2459599999999999E-2</v>
+        <v>0.0134655</v>
       </c>
       <c r="F62">
-        <v>2.2610999999999999E-2</v>
+        <v>0.0304249</v>
       </c>
       <c r="G62">
-        <v>1.684716E-2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01704418</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>68</v>
       </c>
       <c r="B63">
-        <v>1.87464E-2</v>
+        <v>0.0125382</v>
       </c>
       <c r="C63">
-        <v>2.0290300000000001E-2</v>
+        <v>0.0139015</v>
       </c>
       <c r="D63">
-        <v>1.7652899999999999E-2</v>
+        <v>0.0126334</v>
       </c>
       <c r="E63">
-        <v>1.45481E-2</v>
+        <v>0.0132826</v>
       </c>
       <c r="F63">
-        <v>2.0766400000000001E-2</v>
+        <v>0.0328707</v>
       </c>
       <c r="G63">
-        <v>1.8400819999999998E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01704528</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>69</v>
       </c>
       <c r="B64">
-        <v>1.6576899999999999E-2</v>
+        <v>0.0192526</v>
       </c>
       <c r="C64">
-        <v>1.3529100000000001E-2</v>
+        <v>0.0154935</v>
       </c>
       <c r="D64">
-        <v>1.06456E-2</v>
+        <v>0.0122075</v>
       </c>
       <c r="E64">
-        <v>8.7142999999999995E-3</v>
+        <v>0.0103395</v>
       </c>
       <c r="F64">
-        <v>1.45051E-2</v>
+        <v>0.0165577</v>
       </c>
       <c r="G64">
-        <v>1.27942E-2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+        <v>0.01477016</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>70</v>
       </c>
       <c r="B65">
-        <v>1.7382100000000001E-2</v>
+        <v>0.0126882</v>
       </c>
       <c r="C65">
-        <v>1.4164299999999999E-2</v>
+        <v>0.0155169</v>
       </c>
       <c r="D65">
-        <v>1.8060400000000001E-2</v>
+        <v>0.0135893</v>
       </c>
       <c r="E65">
-        <v>1.26508E-2</v>
+        <v>0.0135079</v>
       </c>
       <c r="F65">
-        <v>2.3658599999999998E-2</v>
+        <v>0.030594</v>
       </c>
       <c r="G65">
-        <v>1.7183239999999999E-2</v>
+        <v>0.01717926</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3635,7 +2120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3658,7 +2143,7 @@
         <v>171.2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -3681,7 +2166,7 @@
         <v>171.2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3704,7 +2189,7 @@
         <v>187.6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3727,7 +2212,7 @@
         <v>172.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3750,7 +2235,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3773,7 +2258,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -3796,7 +2281,7 @@
         <v>171.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -3819,7 +2304,7 @@
         <v>177.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -3842,7 +2327,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3865,7 +2350,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3888,7 +2373,7 @@
         <v>171.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3911,7 +2396,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -3934,7 +2419,7 @@
         <v>189.4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -3957,7 +2442,7 @@
         <v>187.6</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3980,7 +2465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -4003,7 +2488,7 @@
         <v>172.8</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -4026,7 +2511,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -4046,10 +2531,10 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>19.600000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -4069,10 +2554,10 @@
         <v>12</v>
       </c>
       <c r="G20">
-        <v>18.600000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -4095,12 +2580,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C22">
         <v>19</v>
@@ -4115,10 +2600,10 @@
         <v>12</v>
       </c>
       <c r="G22">
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -4141,7 +2626,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -4164,7 +2649,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -4187,7 +2672,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -4210,7 +2695,7 @@
         <v>184.4</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -4233,7 +2718,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -4256,7 +2741,7 @@
         <v>181.2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -4270,16 +2755,16 @@
         <v>15</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F29">
         <v>4</v>
       </c>
       <c r="G29">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -4302,7 +2787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -4325,7 +2810,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -4348,7 +2833,7 @@
         <v>187.8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -4371,7 +2856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -4391,10 +2876,10 @@
         <v>15</v>
       </c>
       <c r="G34">
-        <v>20.399999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -4417,7 +2902,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -4437,33 +2922,33 @@
         <v>4</v>
       </c>
       <c r="G36">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C37">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D37">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E37">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F37">
         <v>16</v>
       </c>
       <c r="G37">
-        <v>20.6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -4486,7 +2971,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -4506,10 +2991,10 @@
         <v>15</v>
       </c>
       <c r="G39">
-        <v>19.600000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -4529,10 +3014,10 @@
         <v>15</v>
       </c>
       <c r="G40">
-        <v>20.399999999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -4552,15 +3037,15 @@
         <v>4</v>
       </c>
       <c r="G41">
-        <v>10.199999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C42">
         <v>19</v>
@@ -4572,18 +3057,18 @@
         <v>24</v>
       </c>
       <c r="F42">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G42">
-        <v>20.2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>11</v>
@@ -4598,10 +3083,10 @@
         <v>4</v>
       </c>
       <c r="G43">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -4624,7 +3109,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -4647,7 +3132,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -4670,7 +3155,7 @@
         <v>184.8</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -4693,7 +3178,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -4716,7 +3201,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -4739,7 +3224,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -4750,19 +3235,19 @@
         <v>20</v>
       </c>
       <c r="D50">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E50">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F50">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G50">
-        <v>20.399999999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -4782,10 +3267,10 @@
         <v>16</v>
       </c>
       <c r="G51">
-        <v>20.399999999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -4808,7 +3293,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -4816,45 +3301,45 @@
         <v>18</v>
       </c>
       <c r="C53">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D53">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E53">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F53">
         <v>16</v>
       </c>
       <c r="G53">
-        <v>20.399999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="B54">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C54">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D54">
+        <v>15</v>
+      </c>
+      <c r="E54">
         <v>9</v>
-      </c>
-      <c r="E54">
-        <v>13</v>
       </c>
       <c r="F54">
         <v>4</v>
       </c>
       <c r="G54">
-        <v>10.199999999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -4877,7 +3362,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -4900,7 +3385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -4920,15 +3405,15 @@
         <v>15</v>
       </c>
       <c r="G57">
-        <v>20.399999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="B58">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C58">
         <v>11</v>
@@ -4940,13 +3425,13 @@
         <v>11</v>
       </c>
       <c r="F58">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G58">
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -4969,30 +3454,30 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>65</v>
       </c>
       <c r="B60">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D60">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E60">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F60">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G60">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -5015,30 +3500,30 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="B62">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C62">
         <v>20</v>
       </c>
       <c r="D62">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E62">
         <v>24</v>
       </c>
       <c r="F62">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G62">
-        <v>20.2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -5049,19 +3534,19 @@
         <v>13</v>
       </c>
       <c r="D63">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E63">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G63">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -5084,27 +3569,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>70</v>
       </c>
       <c r="B65">
+        <v>12</v>
+      </c>
+      <c r="C65">
         <v>13</v>
       </c>
-      <c r="C65">
+      <c r="D65">
+        <v>16</v>
+      </c>
+      <c r="E65">
         <v>12</v>
       </c>
-      <c r="D65">
-        <v>13</v>
-      </c>
-      <c r="E65">
-        <v>9</v>
-      </c>
       <c r="F65">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G65">
-        <v>11.4</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -5113,11 +3598,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5140,53 +3625,53 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="C2">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D2">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E2">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F2">
         <v>193.6639969244288</v>
       </c>
       <c r="G2">
-        <v>205.07678195181461</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>205.0767819518146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3">
-        <v>213.23759005323589</v>
+        <v>213.2375900532359</v>
       </c>
       <c r="C3">
         <v>209.3797256769669</v>
       </c>
       <c r="D3">
-        <v>213.23759005323589</v>
+        <v>213.2375900532359</v>
       </c>
       <c r="E3">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="F3">
         <v>193.6639969244288</v>
       </c>
       <c r="G3">
-        <v>205.73952365161151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>205.7395236516115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5194,22 +3679,22 @@
         <v>238.5512985522208</v>
       </c>
       <c r="C4">
-        <v>214.35028842544401</v>
+        <v>214.350288425444</v>
       </c>
       <c r="D4">
-        <v>226.85281374238571</v>
+        <v>226.8528137423857</v>
       </c>
       <c r="E4">
-        <v>201.76450198781711</v>
+        <v>201.7645019878171</v>
       </c>
       <c r="F4">
-        <v>215.92388155425121</v>
+        <v>215.9238815542512</v>
       </c>
       <c r="G4">
-        <v>219.48855685242381</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>219.4885568524238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -5217,275 +3702,275 @@
         <v>217.095454429505</v>
       </c>
       <c r="C5">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D5">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E5">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F5">
         <v>193.6639969244288</v>
       </c>
       <c r="G5">
-        <v>206.01404025201771</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>206.0140402520177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="C6">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D6">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E6">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F6">
         <v>193.6639969244288</v>
       </c>
       <c r="G6">
-        <v>205.07678195181461</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>205.0767819518146</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7">
-        <v>203.56743360951961</v>
+        <v>203.5674336095196</v>
       </c>
       <c r="C7">
         <v>201.6665280368868</v>
       </c>
       <c r="D7">
-        <v>206.20172566370999</v>
+        <v>206.20172566371</v>
       </c>
       <c r="E7">
         <v>193.5523624359607</v>
       </c>
       <c r="F7">
-        <v>187.59291179887489</v>
+        <v>187.5929117988749</v>
       </c>
       <c r="G7">
-        <v>198.51619230899041</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>198.5161923089904</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="C8">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D8">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E8">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F8">
         <v>193.6639969244288</v>
       </c>
       <c r="G8">
-        <v>205.07678195181461</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>205.0767819518146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9">
-        <v>230.35028842544401</v>
+        <v>230.350288425444</v>
       </c>
       <c r="C9">
-        <v>215.17871555019019</v>
+        <v>215.1787155501902</v>
       </c>
       <c r="D9">
-        <v>220.40916292848979</v>
+        <v>220.4091629284898</v>
       </c>
       <c r="E9">
-        <v>200.83556979968259</v>
+        <v>200.8355697996826</v>
       </c>
       <c r="F9">
-        <v>201.86500705120551</v>
+        <v>201.8650070512055</v>
       </c>
       <c r="G9">
-        <v>213.72774875100239</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>213.7277487510024</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="B10">
-        <v>225.13708498984761</v>
+        <v>225.1370849898476</v>
       </c>
       <c r="C10">
-        <v>218.75230867899739</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="D10">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="E10">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="F10">
         <v>203.0365799264593</v>
       </c>
       <c r="G10">
-        <v>212.80571413994909</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>212.8057141399491</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11">
-        <v>203.53379041376451</v>
+        <v>203.5337904137645</v>
       </c>
       <c r="C11">
-        <v>197.61193860700311</v>
+        <v>197.6119386070031</v>
       </c>
       <c r="D11">
-        <v>204.60732654518389</v>
+        <v>204.6073265451839</v>
       </c>
       <c r="E11">
         <v>189.2486212678381</v>
       </c>
       <c r="F11">
-        <v>189.65383485927671</v>
+        <v>189.6538348592767</v>
       </c>
       <c r="G11">
-        <v>196.93110233861319</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>196.9311023386132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
-        <v>213.23759005323589</v>
+        <v>213.2375900532359</v>
       </c>
       <c r="C12">
         <v>209.3797256769669</v>
       </c>
       <c r="D12">
-        <v>213.23759005323589</v>
+        <v>213.2375900532359</v>
       </c>
       <c r="E12">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="F12">
         <v>193.6639969244288</v>
       </c>
       <c r="G12">
-        <v>205.73952365161151</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>205.7395236516115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13">
-        <v>219.46870128378359</v>
+        <v>219.4687012837836</v>
       </c>
       <c r="C13">
-        <v>204.51616349626769</v>
+        <v>204.5161634962677</v>
       </c>
       <c r="D13">
-        <v>219.24876739829651</v>
+        <v>219.2487673982965</v>
       </c>
       <c r="E13">
-        <v>192.06714970508381</v>
+        <v>192.0671497050838</v>
       </c>
       <c r="F13">
-        <v>193.98289739239689</v>
+        <v>193.9828973923969</v>
       </c>
       <c r="G13">
-        <v>205.85673585516571</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>205.8567358551657</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14">
-        <v>242.69343417595161</v>
+        <v>242.6934341759516</v>
       </c>
       <c r="C14">
-        <v>214.35028842544401</v>
+        <v>214.350288425444</v>
       </c>
       <c r="D14">
-        <v>237.29646455628159</v>
+        <v>237.2964645562816</v>
       </c>
       <c r="E14">
-        <v>201.17871555019019</v>
+        <v>201.1787155501902</v>
       </c>
       <c r="F14">
         <v>212.9949493661166</v>
       </c>
       <c r="G14">
-        <v>221.70277041479679</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>221.7027704147968</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15">
-        <v>237.72287142747459</v>
+        <v>237.7228714274746</v>
       </c>
       <c r="C15">
-        <v>218.75230867899739</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="D15">
-        <v>221.33809511662429</v>
+        <v>221.3380951166243</v>
       </c>
       <c r="E15">
         <v>198.9360748630709</v>
       </c>
       <c r="F15">
-        <v>215.72287142747459</v>
+        <v>215.7228714274746</v>
       </c>
       <c r="G15">
-        <v>218.49444430272831</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>218.4944443027283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16">
-        <v>208.25232218308409</v>
+        <v>208.2523221830841</v>
       </c>
       <c r="C16">
-        <v>198.93034199038169</v>
+        <v>198.9303419903817</v>
       </c>
       <c r="D16">
-        <v>203.62020384855049</v>
+        <v>203.6202038485505</v>
       </c>
       <c r="E16">
-        <v>186.49127209070201</v>
+        <v>186.491272090702</v>
       </c>
       <c r="F16">
-        <v>187.34398902518191</v>
+        <v>187.3439890251819</v>
       </c>
       <c r="G16">
         <v>196.9276258275801</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -5493,56 +3978,56 @@
         <v>217.095454429505</v>
       </c>
       <c r="C17">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D17">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E17">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F17">
         <v>193.6639969244288</v>
       </c>
       <c r="G17">
-        <v>206.01404025201771</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>206.0140402520177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="C18">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D18">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E18">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F18">
         <v>193.6639969244288</v>
       </c>
       <c r="G18">
-        <v>205.07678195181461</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>205.0767819518146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19">
-        <v>224.55129855222069</v>
+        <v>224.5512985522207</v>
       </c>
       <c r="C19">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D19">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E19">
         <v>203.0365799264593</v>
@@ -5551,10 +4036,10 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G19">
-        <v>212.19150057757611</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>212.1915005775761</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -5562,22 +4047,22 @@
         <v>217.095454429505</v>
       </c>
       <c r="C20">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D20">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E20">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F20">
         <v>193.6639969244288</v>
       </c>
       <c r="G20">
-        <v>206.01404025201771</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>206.0140402520177</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -5585,214 +4070,214 @@
         <v>209.5588335705169</v>
       </c>
       <c r="C21">
-        <v>205.82904579473271</v>
+        <v>205.8290457947327</v>
       </c>
       <c r="D21">
         <v>211.062613349125</v>
       </c>
       <c r="E21">
-        <v>194.81313863108201</v>
+        <v>194.813138631082</v>
       </c>
       <c r="F21">
-        <v>191.54499915195851</v>
+        <v>191.5449991519585</v>
       </c>
       <c r="G21">
         <v>202.561726099483</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22">
-        <v>224.55129855222069</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="C22">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D22">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E22">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F22">
         <v>193.6639969244288</v>
       </c>
       <c r="G22">
-        <v>207.50520907656079</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>205.0767819518146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23">
-        <v>204.99484092581631</v>
+        <v>204.9948409258163</v>
       </c>
       <c r="C23">
-        <v>201.30769961265111</v>
+        <v>201.3076996126511</v>
       </c>
       <c r="D23">
-        <v>204.98245579924691</v>
+        <v>204.9824557992469</v>
       </c>
       <c r="E23">
-        <v>193.05283202541881</v>
+        <v>193.0528320254188</v>
       </c>
       <c r="F23">
-        <v>187.68557856104229</v>
+        <v>187.6855785610423</v>
       </c>
       <c r="G23">
         <v>198.4046813848351</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>29</v>
       </c>
       <c r="B24">
-        <v>217.27422687349181</v>
+        <v>217.2742268734918</v>
       </c>
       <c r="C24">
-        <v>203.16961391690279</v>
+        <v>203.1696139169028</v>
       </c>
       <c r="D24">
-        <v>216.31798086904371</v>
+        <v>216.3179808690437</v>
       </c>
       <c r="E24">
-        <v>192.39513529856291</v>
+        <v>192.3951352985629</v>
       </c>
       <c r="F24">
         <v>188.8474884458995</v>
       </c>
       <c r="G24">
-        <v>203.60088908078009</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>203.6008890807801</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25">
-        <v>234.49242404917501</v>
+        <v>234.492424049175</v>
       </c>
       <c r="C25">
-        <v>214.35028842544401</v>
+        <v>214.350288425444</v>
       </c>
       <c r="D25">
-        <v>230.26702730475881</v>
+        <v>230.2670273047588</v>
       </c>
       <c r="E25">
-        <v>200.0071426749364</v>
+        <v>200.8355697996826</v>
       </c>
       <c r="F25">
         <v>198.9360748630709</v>
       </c>
       <c r="G25">
-        <v>215.61059146347699</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>215.7762768884263</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>31</v>
       </c>
       <c r="B26">
-        <v>225.72287142747459</v>
+        <v>225.7228714274746</v>
       </c>
       <c r="C26">
-        <v>219.58073580374361</v>
+        <v>219.5807358037436</v>
       </c>
       <c r="D26">
-        <v>219.58073580374361</v>
+        <v>219.5807358037436</v>
       </c>
       <c r="E26">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="F26">
-        <v>213.23759005323589</v>
+        <v>213.2375900532359</v>
       </c>
       <c r="G26">
-        <v>215.46012972767761</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>215.4601297276776</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>32</v>
       </c>
       <c r="B27">
-        <v>215.56951641940859</v>
+        <v>215.5695164194086</v>
       </c>
       <c r="C27">
-        <v>207.42488285544599</v>
+        <v>207.424882855446</v>
       </c>
       <c r="D27">
-        <v>208.24061365691611</v>
+        <v>208.2406136569161</v>
       </c>
       <c r="E27">
-        <v>191.04858571919809</v>
+        <v>191.0485857191981</v>
       </c>
       <c r="F27">
-        <v>192.50162478257309</v>
+        <v>192.5016247825731</v>
       </c>
       <c r="G27">
         <v>202.9570446867084</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>33</v>
       </c>
       <c r="B28">
-        <v>228.20815280171311</v>
+        <v>228.2081528017131</v>
       </c>
       <c r="C28">
-        <v>218.75230867899739</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="D28">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="E28">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="F28">
         <v>203.0365799264593</v>
       </c>
       <c r="G28">
-        <v>213.41992770232221</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>213.4199277023222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29">
-        <v>204.99484092581631</v>
+        <v>204.9948409258163</v>
       </c>
       <c r="C29">
-        <v>197.9415538688763</v>
+        <v>197.8808445278704</v>
       </c>
       <c r="D29">
-        <v>205.49070842301589</v>
+        <v>205.4907084230159</v>
       </c>
       <c r="E29">
-        <v>190.8044325344818</v>
+        <v>192.9407642197364</v>
       </c>
       <c r="F29">
-        <v>187.34398902518191</v>
+        <v>187.3439890251819</v>
       </c>
       <c r="G29">
-        <v>197.3151049554744</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>197.7302294243242</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30">
-        <v>227.91146908650501</v>
+        <v>227.911469086505</v>
       </c>
       <c r="C30">
-        <v>206.40962072616639</v>
+        <v>206.4096207261664</v>
       </c>
       <c r="D30">
         <v>222.1080327222457</v>
@@ -5801,24 +4286,24 @@
         <v>192.0991124527755</v>
       </c>
       <c r="F30">
-        <v>193.98289739239689</v>
+        <v>193.9828973923969</v>
       </c>
       <c r="G30">
-        <v>208.50222647601791</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>208.5022264760179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="B31">
-        <v>221.77644583206941</v>
+        <v>221.7764458320694</v>
       </c>
       <c r="C31">
-        <v>209.67674266387999</v>
+        <v>209.67674266388</v>
       </c>
       <c r="D31">
-        <v>211.73407903147461</v>
+        <v>211.7340790314746</v>
       </c>
       <c r="E31">
         <v>192.0991124527755</v>
@@ -5827,70 +4312,70 @@
         <v>198.709949036832</v>
       </c>
       <c r="G31">
-        <v>206.79926580340631</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>206.7992658034063</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32">
-        <v>232.75230867899739</v>
+        <v>232.7523086789974</v>
       </c>
       <c r="C32">
-        <v>218.75230867899739</v>
+        <v>218.7523086789974</v>
       </c>
       <c r="D32">
         <v>224.9949493661166</v>
       </c>
       <c r="E32">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F32">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="G32">
-        <v>217.45180361560909</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>217.4518036156091</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33">
-        <v>208.25232218308409</v>
+        <v>208.2523221830841</v>
       </c>
       <c r="C33">
-        <v>198.93034199038169</v>
+        <v>198.9303419903817</v>
       </c>
       <c r="D33">
-        <v>203.62020384855049</v>
+        <v>203.6202038485505</v>
       </c>
       <c r="E33">
-        <v>186.49127209070201</v>
+        <v>186.491272090702</v>
       </c>
       <c r="F33">
-        <v>187.34398902518191</v>
+        <v>187.3439890251819</v>
       </c>
       <c r="G33">
         <v>196.9276258275801</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>39</v>
       </c>
       <c r="B34">
-        <v>266.45079348883229</v>
+        <v>266.4507934888323</v>
       </c>
       <c r="C34">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D34">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E34">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F34">
         <v>203.0365799264593</v>
@@ -5899,30 +4384,30 @@
         <v>219.6341412646953</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="B35">
-        <v>224.55129855222069</v>
+        <v>224.5512985522207</v>
       </c>
       <c r="C35">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D35">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="E35">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F35">
         <v>203.0365799264593</v>
       </c>
       <c r="G35">
-        <v>212.35718600252531</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>212.3571860025253</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -5939,50 +4424,50 @@
         <v>192.6542644043582</v>
       </c>
       <c r="F36">
-        <v>187.34398902518191</v>
+        <v>187.3439890251819</v>
       </c>
       <c r="G36">
-        <v>198.87484019464429</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>198.8748401946443</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37">
-        <v>224.55129855222069</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="C37">
-        <v>233.63961030678931</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D37">
-        <v>221.7817459305202</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E37">
-        <v>251.27922061357859</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F37">
         <v>193.6639969244288</v>
       </c>
       <c r="G37">
-        <v>224.98317446550749</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>205.0767819518146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>43</v>
       </c>
       <c r="B38">
-        <v>221.70096919424779</v>
+        <v>221.7009691942478</v>
       </c>
       <c r="C38">
-        <v>214.08984039418249</v>
+        <v>214.0898403941825</v>
       </c>
       <c r="D38">
         <v>211.062613349125</v>
       </c>
       <c r="E38">
-        <v>196.56376190917649</v>
+        <v>196.5637619091765</v>
       </c>
       <c r="F38">
         <v>196.5117868477252</v>
@@ -5991,18 +4476,18 @@
         <v>207.9857943388914</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39">
-        <v>224.55129855222069</v>
+        <v>224.5512985522207</v>
       </c>
       <c r="C39">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D39">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E39">
         <v>203.0365799264593</v>
@@ -6011,24 +4496,24 @@
         <v>203.0365799264593</v>
       </c>
       <c r="G39">
-        <v>212.19150057757611</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>212.1915005775761</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>45</v>
       </c>
       <c r="B40">
-        <v>224.55129855222069</v>
+        <v>224.5512985522207</v>
       </c>
       <c r="C40">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D40">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="E40">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="F40">
         <v>203.0365799264593</v>
@@ -6037,7 +4522,7 @@
         <v>214.3973880278806</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -6045,105 +4530,105 @@
         <v>214.2451250715321</v>
       </c>
       <c r="C41">
-        <v>205.82904579473271</v>
+        <v>205.8290457947327</v>
       </c>
       <c r="D41">
         <v>211.062613349125</v>
       </c>
       <c r="E41">
-        <v>190.09446361390371</v>
+        <v>190.0944636139037</v>
       </c>
       <c r="F41">
-        <v>191.54499915195851</v>
+        <v>191.5449991519585</v>
       </c>
       <c r="G41">
-        <v>202.55524939625039</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>202.5552493962504</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42">
-        <v>224.55129855222069</v>
+        <v>217.095454429505</v>
       </c>
       <c r="C42">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="D42">
-        <v>212.40916292848979</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E42">
-        <v>198.35028842544401</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F42">
-        <v>203.0365799264593</v>
+        <v>193.6639969244288</v>
       </c>
       <c r="G42">
-        <v>209.3797256769669</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>206.0140402520177</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43">
-        <v>221.70096919424779</v>
+        <v>209.5588335705169</v>
       </c>
       <c r="C43">
-        <v>205.82904579473271</v>
+        <v>205.8290457947327</v>
       </c>
       <c r="D43">
         <v>211.062613349125</v>
       </c>
       <c r="E43">
-        <v>194.81313863108201</v>
+        <v>194.813138631082</v>
       </c>
       <c r="F43">
-        <v>191.54499915195851</v>
+        <v>191.5449991519585</v>
       </c>
       <c r="G43">
-        <v>204.9901532242292</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>202.561726099483</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44">
-        <v>225.71699467621309</v>
+        <v>225.7169946762131</v>
       </c>
       <c r="C44">
-        <v>205.15588556365569</v>
+        <v>205.1558855636557</v>
       </c>
       <c r="D44">
         <v>219.4050796727812</v>
       </c>
       <c r="E44">
-        <v>192.80645083145859</v>
+        <v>192.528335978423</v>
       </c>
       <c r="F44">
         <v>188.8474884458995</v>
       </c>
       <c r="G44">
-        <v>206.3863798380016</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>206.3307568673945</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>50</v>
       </c>
       <c r="B45">
-        <v>219.58197142177761</v>
+        <v>219.5819714217776</v>
       </c>
       <c r="C45">
-        <v>209.36663344984279</v>
+        <v>209.3666334498428</v>
       </c>
       <c r="D45">
-        <v>211.29746103441209</v>
+        <v>211.2974610344121</v>
       </c>
       <c r="E45">
-        <v>192.39513529856291</v>
+        <v>192.3951352985629</v>
       </c>
       <c r="F45">
         <v>198.709949036832</v>
@@ -6152,136 +4637,136 @@
         <v>206.2702300482855</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46">
-        <v>225.72287142747459</v>
+        <v>225.7228714274746</v>
       </c>
       <c r="C46">
-        <v>219.58073580374361</v>
+        <v>219.5807358037436</v>
       </c>
       <c r="D46">
-        <v>223.23759005323589</v>
+        <v>223.2375900532359</v>
       </c>
       <c r="E46">
-        <v>199.17871555019019</v>
+        <v>199.1787155501902</v>
       </c>
       <c r="F46">
-        <v>213.23759005323589</v>
+        <v>213.2375900532359</v>
       </c>
       <c r="G46">
-        <v>216.19150057757599</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>216.191500577576</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>52</v>
       </c>
       <c r="B47">
-        <v>215.56951641940859</v>
+        <v>215.5695164194086</v>
       </c>
       <c r="C47">
-        <v>207.42488285544599</v>
+        <v>207.424882855446</v>
       </c>
       <c r="D47">
-        <v>208.24061365691611</v>
+        <v>208.2406136569161</v>
       </c>
       <c r="E47">
-        <v>191.04858571919809</v>
+        <v>191.0485857191981</v>
       </c>
       <c r="F47">
-        <v>192.50162478257309</v>
+        <v>192.5016247825731</v>
       </c>
       <c r="G47">
         <v>202.9570446867084</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="B48">
-        <v>221.77644583206941</v>
+        <v>221.7764458320694</v>
       </c>
       <c r="C48">
-        <v>209.67674266387999</v>
+        <v>209.67674266388</v>
       </c>
       <c r="D48">
-        <v>213.87174654405101</v>
+        <v>213.871746544051</v>
       </c>
       <c r="E48">
-        <v>192.03828591093071</v>
+        <v>192.0382859109307</v>
       </c>
       <c r="F48">
-        <v>200.54029573372509</v>
+        <v>200.5402957337251</v>
       </c>
       <c r="G48">
-        <v>207.58070333693121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>207.5807033369312</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>54</v>
       </c>
       <c r="B49">
-        <v>230.37121064084829</v>
+        <v>230.3712106408483</v>
       </c>
       <c r="C49">
-        <v>211.04304927991731</v>
+        <v>211.0430492799173</v>
       </c>
       <c r="D49">
-        <v>208.36951419039531</v>
+        <v>208.3695141903953</v>
       </c>
       <c r="E49">
-        <v>188.67305645252739</v>
+        <v>188.6730564525274</v>
       </c>
       <c r="F49">
-        <v>193.67963962498649</v>
+        <v>193.6796396249865</v>
       </c>
       <c r="G49">
-        <v>206.42729403773501</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+        <v>206.427294037735</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="B50">
-        <v>271.96551211459382</v>
+        <v>266.4507934888323</v>
       </c>
       <c r="C50">
-        <v>214.0660171779821</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D50">
-        <v>254.61017305526639</v>
+        <v>212.4091629284898</v>
       </c>
       <c r="E50">
-        <v>218.4507934888324</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F50">
-        <v>193.6639969244288</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G50">
-        <v>230.55129855222069</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>219.6341412646953</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>56</v>
       </c>
       <c r="B51">
-        <v>224.55129855222069</v>
+        <v>224.5512985522207</v>
       </c>
       <c r="C51">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D51">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="E51">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="F51">
         <v>203.0365799264593</v>
@@ -6290,18 +4775,18 @@
         <v>214.3973880278806</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>57</v>
       </c>
       <c r="B52">
-        <v>222.17022109767589</v>
+        <v>222.1702210976759</v>
       </c>
       <c r="C52">
-        <v>211.04304927991731</v>
+        <v>211.0430492799173</v>
       </c>
       <c r="D52">
-        <v>214.33647357812561</v>
+        <v>214.3364735781256</v>
       </c>
       <c r="E52">
         <v>192.6542644043582</v>
@@ -6313,67 +4798,67 @@
         <v>206.5029570162051</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>58</v>
       </c>
       <c r="B53">
-        <v>224.55129855222069</v>
+        <v>224.5512985522207</v>
       </c>
       <c r="C53">
-        <v>239.96551211459379</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D53">
-        <v>212.40916292848979</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="E53">
-        <v>203.8650070512054</v>
+        <v>198.350288425444</v>
       </c>
       <c r="F53">
-        <v>193.6639969244288</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G53">
-        <v>214.89099551418769</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+        <v>212.3571860025253</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="B54">
-        <v>220.0512233252056</v>
+        <v>205.5007992866575</v>
       </c>
       <c r="C54">
-        <v>227.85829715105589</v>
+        <v>202.6246318390989</v>
       </c>
       <c r="D54">
-        <v>215.38939181604201</v>
+        <v>206.2505164179251</v>
       </c>
       <c r="E54">
-        <v>231.76172255520379</v>
+        <v>192.6542644043582</v>
       </c>
       <c r="F54">
-        <v>187.34398902518191</v>
+        <v>187.3439890251819</v>
       </c>
       <c r="G54">
-        <v>216.48092477453781</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+        <v>198.8748401946443</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>60</v>
       </c>
       <c r="B55">
-        <v>221.70096919424779</v>
+        <v>221.7009691942478</v>
       </c>
       <c r="C55">
-        <v>214.08984039418249</v>
+        <v>214.0898403941825</v>
       </c>
       <c r="D55">
         <v>211.062613349125</v>
       </c>
       <c r="E55">
-        <v>196.56376190917649</v>
+        <v>196.5637619091765</v>
       </c>
       <c r="F55">
         <v>196.5117868477252</v>
@@ -6382,18 +4867,18 @@
         <v>207.9857943388914</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>61</v>
       </c>
       <c r="B56">
-        <v>221.70096919424779</v>
+        <v>221.7009691942478</v>
       </c>
       <c r="C56">
-        <v>214.08984039418249</v>
+        <v>214.0898403941825</v>
       </c>
       <c r="D56">
-        <v>216.57733197488639</v>
+        <v>216.5773319748864</v>
       </c>
       <c r="E56">
         <v>201.3376443991751</v>
@@ -6402,24 +4887,24 @@
         <v>196.5117868477252</v>
       </c>
       <c r="G56">
-        <v>210.04351456204341</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+        <v>210.0435145620434</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>62</v>
       </c>
       <c r="B57">
-        <v>224.55129855222069</v>
+        <v>224.5512985522207</v>
       </c>
       <c r="C57">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D57">
-        <v>217.92388155425121</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="E57">
-        <v>208.55129855222069</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="F57">
         <v>203.0365799264593</v>
@@ -6428,90 +4913,90 @@
         <v>214.3973880278806</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="B58">
-        <v>221.70096919424779</v>
+        <v>214.2451250715321</v>
       </c>
       <c r="C58">
-        <v>205.82904579473271</v>
+        <v>205.8290457947327</v>
       </c>
       <c r="D58">
         <v>211.062613349125</v>
       </c>
       <c r="E58">
-        <v>190.09446361390371</v>
+        <v>190.0944636139037</v>
       </c>
       <c r="F58">
-        <v>196.5117868477252</v>
+        <v>191.5449991519585</v>
       </c>
       <c r="G58">
-        <v>205.03977575994679</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+        <v>202.5552493962504</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>64</v>
       </c>
       <c r="B59">
-        <v>219.58197142177761</v>
+        <v>219.5819714217776</v>
       </c>
       <c r="C59">
-        <v>209.36663344984279</v>
+        <v>209.3666334498428</v>
       </c>
       <c r="D59">
-        <v>213.43512854698861</v>
+        <v>213.4351285469886</v>
       </c>
       <c r="E59">
-        <v>192.39513529856291</v>
+        <v>192.3951352985629</v>
       </c>
       <c r="F59">
-        <v>200.54029573372509</v>
+        <v>200.5402957337251</v>
       </c>
       <c r="G59">
-        <v>207.06383289017941</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+        <v>207.0638328901794</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>65</v>
       </c>
       <c r="B60">
-        <v>237.25557116600561</v>
+        <v>230.3712106408483</v>
       </c>
       <c r="C60">
-        <v>211.04877549728519</v>
+        <v>211.0430492799173</v>
       </c>
       <c r="D60">
-        <v>250.8077936418064</v>
+        <v>208.3695141903953</v>
       </c>
       <c r="E60">
-        <v>202.29805811351909</v>
+        <v>188.6730564525274</v>
       </c>
       <c r="F60">
-        <v>187.34398902518191</v>
+        <v>193.6796396249865</v>
       </c>
       <c r="G60">
-        <v>217.7508374887596</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+        <v>206.427294037735</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>66</v>
       </c>
       <c r="B61">
-        <v>222.17022109767589</v>
+        <v>222.1702210976759</v>
       </c>
       <c r="C61">
-        <v>211.04304927991731</v>
+        <v>211.0430492799173</v>
       </c>
       <c r="D61">
-        <v>214.33647357812561</v>
+        <v>214.3364735781256</v>
       </c>
       <c r="E61">
-        <v>199.17877017245129</v>
+        <v>199.1787701724513</v>
       </c>
       <c r="F61">
         <v>192.3107767209485</v>
@@ -6520,64 +5005,64 @@
         <v>207.8078581698237</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="B62">
-        <v>255.96551211459379</v>
+        <v>224.5512985522207</v>
       </c>
       <c r="C62">
-        <v>214.0660171779821</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="D62">
-        <v>212.40916292848979</v>
+        <v>217.9238815542512</v>
       </c>
       <c r="E62">
-        <v>218.4507934888324</v>
+        <v>208.5512985522207</v>
       </c>
       <c r="F62">
-        <v>227.29646455628159</v>
+        <v>203.0365799264593</v>
       </c>
       <c r="G62">
-        <v>225.6375900532359</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+        <v>214.3973880278806</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>68</v>
       </c>
       <c r="B63">
-        <v>220.0512233252056</v>
+        <v>222.1702210976759</v>
       </c>
       <c r="C63">
-        <v>209.604943347925</v>
+        <v>211.0430492799173</v>
       </c>
       <c r="D63">
-        <v>206.04065069635189</v>
+        <v>214.3364735781256</v>
       </c>
       <c r="E63">
-        <v>197.51571612753321</v>
+        <v>192.6542644043582</v>
       </c>
       <c r="F63">
-        <v>187.34398902518191</v>
+        <v>192.3107767209485</v>
       </c>
       <c r="G63">
-        <v>204.11130450443949</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+        <v>206.5029570162051</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>69</v>
       </c>
       <c r="B64">
-        <v>221.70096919424779</v>
+        <v>221.7009691942478</v>
       </c>
       <c r="C64">
-        <v>214.08984039418249</v>
+        <v>214.0898403941825</v>
       </c>
       <c r="D64">
-        <v>216.57733197488639</v>
+        <v>216.5773319748864</v>
       </c>
       <c r="E64">
         <v>201.3376443991751</v>
@@ -6586,30 +5071,30 @@
         <v>196.5117868477252</v>
       </c>
       <c r="G64">
-        <v>210.04351456204341</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+        <v>210.0435145620434</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>70</v>
       </c>
       <c r="B65">
-        <v>237.20144063955729</v>
+        <v>222.1702210976759</v>
       </c>
       <c r="C65">
-        <v>211.04877549728519</v>
+        <v>211.0430492799173</v>
       </c>
       <c r="D65">
-        <v>206.04065069635189</v>
+        <v>214.3364735781256</v>
       </c>
       <c r="E65">
-        <v>202.29805811351909</v>
+        <v>199.1787701724513</v>
       </c>
       <c r="F65">
-        <v>220.9764566570347</v>
+        <v>192.3107767209485</v>
       </c>
       <c r="G65">
-        <v>215.5130763207496</v>
+        <v>207.8078581698237</v>
       </c>
     </row>
   </sheetData>
@@ -6618,11 +5103,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6645,7 +5130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -6665,10 +5150,10 @@
         <v>1281</v>
       </c>
       <c r="G2">
-        <v>639.79999999999995</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>639.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -6691,7 +5176,7 @@
         <v>762.4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -6714,7 +5199,7 @@
         <v>558.6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -6737,7 +5222,7 @@
         <v>501.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -6760,7 +5245,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -6780,33 +5265,33 @@
         <v>1281</v>
       </c>
       <c r="G7">
-        <v>639.79999999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>639.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C8">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="D8">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E8">
-        <v>744</v>
+        <v>706</v>
       </c>
       <c r="F8">
-        <v>1079</v>
+        <v>1042</v>
       </c>
       <c r="G8">
-        <v>560.6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>540.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -6829,7 +5314,7 @@
         <v>586.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -6852,7 +5337,7 @@
         <v>485.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -6875,30 +5360,30 @@
         <v>762.4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C12">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="D12">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E12">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="F12">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G12">
-        <v>616.20000000000005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>607.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6921,30 +5406,30 @@
         <v>558.6</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="C14">
-        <v>696</v>
+        <v>673</v>
       </c>
       <c r="D14">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="E14">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="F14">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G14">
-        <v>555.20000000000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>543.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -6964,10 +5449,10 @@
         <v>594</v>
       </c>
       <c r="G15">
-        <v>530.20000000000005</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>530.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -6990,30 +5475,30 @@
         <v>501.8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C17">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="D17">
         <v>283</v>
       </c>
       <c r="E17">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="F17">
-        <v>935</v>
+        <v>872</v>
       </c>
       <c r="G17">
-        <v>562.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>540.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -7033,10 +5518,10 @@
         <v>18</v>
       </c>
       <c r="G18">
-        <v>17.399999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -7059,7 +5544,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -7082,7 +5567,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -7105,53 +5590,53 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22">
+        <v>11</v>
+      </c>
+      <c r="C22">
+        <v>14</v>
+      </c>
+      <c r="D22">
+        <v>9</v>
+      </c>
+      <c r="E22">
+        <v>22</v>
+      </c>
+      <c r="F22">
         <v>12</v>
       </c>
-      <c r="C22">
-        <v>15</v>
-      </c>
-      <c r="D22">
-        <v>11</v>
-      </c>
-      <c r="E22">
-        <v>23</v>
-      </c>
-      <c r="F22">
-        <v>13</v>
-      </c>
       <c r="G22">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C23">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="D23">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E23">
-        <v>744</v>
+        <v>706</v>
       </c>
       <c r="F23">
-        <v>1079</v>
+        <v>1042</v>
       </c>
       <c r="G23">
-        <v>560.6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>540.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -7174,30 +5659,30 @@
         <v>586.4</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C25">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="D25">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E25">
-        <v>718</v>
+        <v>641</v>
       </c>
       <c r="F25">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G25">
-        <v>567.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>547.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -7220,7 +5705,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -7243,7 +5728,7 @@
         <v>485.2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -7251,68 +5736,68 @@
         <v>429</v>
       </c>
       <c r="C28">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D28">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="E28">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="F28">
-        <v>743</v>
+        <v>685</v>
       </c>
       <c r="G28">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>491.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C29">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="D29">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E29">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="F29">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G29">
-        <v>616.20000000000005</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>607.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="C30">
-        <v>696</v>
+        <v>673</v>
       </c>
       <c r="D30">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="E30">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="F30">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G30">
-        <v>555.20000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>543.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -7332,56 +5817,56 @@
         <v>594</v>
       </c>
       <c r="G31">
-        <v>530.20000000000005</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+        <v>530.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C32">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="D32">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E32">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F32">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="G32">
-        <v>541.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>534.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>38</v>
       </c>
       <c r="B33">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C33">
-        <v>648</v>
+        <v>617</v>
       </c>
       <c r="D33">
         <v>283</v>
       </c>
       <c r="E33">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="F33">
-        <v>935</v>
+        <v>872</v>
       </c>
       <c r="G33">
-        <v>562.4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>540.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -7404,7 +5889,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -7424,10 +5909,10 @@
         <v>19</v>
       </c>
       <c r="G35">
-        <v>18.600000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -7447,10 +5932,10 @@
         <v>18</v>
       </c>
       <c r="G36">
-        <v>17.399999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -7458,22 +5943,22 @@
         <v>17</v>
       </c>
       <c r="C37">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D37">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E37">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G37">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -7496,12 +5981,12 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C39">
         <v>16</v>
@@ -7516,10 +6001,10 @@
         <v>8</v>
       </c>
       <c r="G39">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -7542,7 +6027,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -7565,12 +6050,12 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C42">
         <v>16</v>
@@ -7582,59 +6067,59 @@
         <v>25</v>
       </c>
       <c r="F42">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G42">
-        <v>16.600000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43">
+        <v>11</v>
+      </c>
+      <c r="C43">
+        <v>14</v>
+      </c>
+      <c r="D43">
+        <v>9</v>
+      </c>
+      <c r="E43">
+        <v>22</v>
+      </c>
+      <c r="F43">
         <v>12</v>
       </c>
-      <c r="C43">
-        <v>15</v>
-      </c>
-      <c r="D43">
-        <v>11</v>
-      </c>
-      <c r="E43">
-        <v>23</v>
-      </c>
-      <c r="F43">
-        <v>13</v>
-      </c>
       <c r="G43">
-        <v>14.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C44">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="D44">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E44">
-        <v>718</v>
+        <v>641</v>
       </c>
       <c r="F44">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G44">
-        <v>567.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>547.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -7657,30 +6142,30 @@
         <v>503</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="C46">
         <v>518</v>
       </c>
       <c r="D46">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E46">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F46">
         <v>676</v>
       </c>
       <c r="G46">
-        <v>551.20000000000005</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>546.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -7688,45 +6173,45 @@
         <v>429</v>
       </c>
       <c r="C47">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D47">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="E47">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="F47">
-        <v>743</v>
+        <v>685</v>
       </c>
       <c r="G47">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>491.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="B48">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="C48">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="D48">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E48">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F48">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="G48">
-        <v>541.4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>534.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -7749,30 +6234,30 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="B50">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C50">
+        <v>17</v>
+      </c>
+      <c r="D50">
+        <v>14</v>
+      </c>
+      <c r="E50">
         <v>22</v>
-      </c>
-      <c r="D50">
-        <v>15</v>
-      </c>
-      <c r="E50">
-        <v>27</v>
       </c>
       <c r="F50">
         <v>15</v>
       </c>
       <c r="G50">
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -7792,10 +6277,10 @@
         <v>18</v>
       </c>
       <c r="G51">
-        <v>18.600000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -7815,33 +6300,33 @@
         <v>19</v>
       </c>
       <c r="G52">
-        <v>18.600000000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>58</v>
       </c>
       <c r="B53">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C53">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D53">
         <v>19</v>
       </c>
       <c r="E53">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F53">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G53">
-        <v>19.399999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -7849,27 +6334,27 @@
         <v>17</v>
       </c>
       <c r="C54">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D54">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E54">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F54">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G54">
-        <v>22.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>60</v>
       </c>
       <c r="B55">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C55">
         <v>16</v>
@@ -7884,10 +6369,10 @@
         <v>8</v>
       </c>
       <c r="G55">
-        <v>12.8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -7910,7 +6395,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -7933,12 +6418,12 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="B58">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C58">
         <v>16</v>
@@ -7950,59 +6435,59 @@
         <v>25</v>
       </c>
       <c r="F58">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G58">
-        <v>16.600000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>64</v>
       </c>
       <c r="B59">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="C59">
         <v>518</v>
       </c>
       <c r="D59">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E59">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F59">
         <v>676</v>
       </c>
       <c r="G59">
-        <v>551.20000000000005</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+        <v>546.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>65</v>
       </c>
       <c r="B60">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C60">
+        <v>17</v>
+      </c>
+      <c r="D60">
+        <v>14</v>
+      </c>
+      <c r="E60">
         <v>22</v>
-      </c>
-      <c r="D60">
-        <v>15</v>
-      </c>
-      <c r="E60">
-        <v>27</v>
       </c>
       <c r="F60">
         <v>15</v>
       </c>
       <c r="G60">
-        <v>18.8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -8022,56 +6507,56 @@
         <v>18</v>
       </c>
       <c r="G61">
-        <v>18.600000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="B62">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C62">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D62">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E62">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F62">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G62">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>68</v>
       </c>
       <c r="B63">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C63">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D63">
         <v>19</v>
       </c>
       <c r="E63">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F63">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G63">
-        <v>19.399999999999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -8094,27 +6579,27 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>70</v>
       </c>
       <c r="B65">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C65">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D65">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E65">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F65">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G65">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
     </row>
   </sheetData>
@@ -8123,11 +6608,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8150,7 +6635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -8170,10 +6655,10 @@
         <v>4902</v>
       </c>
       <c r="G2">
-        <v>4764.6000000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4764.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -8196,7 +6681,7 @@
         <v>3378.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -8219,7 +6704,7 @@
         <v>1383.2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -8242,7 +6727,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -8265,7 +6750,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -8285,10 +6770,10 @@
         <v>4902</v>
       </c>
       <c r="G7">
-        <v>4764.6000000000004</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4764.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -8308,10 +6793,10 @@
         <v>5069</v>
       </c>
       <c r="G8">
-        <v>4845.3999999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4845.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -8334,7 +6819,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -8357,7 +6842,7 @@
         <v>2654.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -8380,30 +6865,30 @@
         <v>3378.8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
-        <v>4270</v>
+        <v>4269</v>
       </c>
       <c r="C12">
-        <v>3493</v>
+        <v>3486</v>
       </c>
       <c r="D12">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="E12">
-        <v>3469</v>
+        <v>3472</v>
       </c>
       <c r="F12">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="G12">
-        <v>3306.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>3304.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -8426,30 +6911,30 @@
         <v>1383.2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="C14">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="D14">
         <v>1622</v>
       </c>
       <c r="E14">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F14">
         <v>378</v>
       </c>
       <c r="G14">
-        <v>1498</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1497.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -8472,7 +6957,7 @@
         <v>1632.2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -8495,7 +6980,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -8518,7 +7003,7 @@
         <v>3190.6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -8541,7 +7026,7 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -8564,7 +7049,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -8587,7 +7072,7 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -8610,30 +7095,30 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D22">
         <v>61</v>
       </c>
       <c r="E22">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F22">
         <v>29</v>
       </c>
       <c r="G22">
-        <v>50.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -8653,10 +7138,10 @@
         <v>5069</v>
       </c>
       <c r="G23">
-        <v>4845.3999999999996</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4845.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -8679,30 +7164,30 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="C25">
-        <v>2107</v>
+        <v>2111</v>
       </c>
       <c r="D25">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="E25">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="F25">
         <v>245</v>
       </c>
       <c r="G25">
-        <v>1376.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1367.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -8725,7 +7210,7 @@
         <v>1526.6</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -8748,7 +7233,7 @@
         <v>2654.2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -8756,68 +7241,68 @@
         <v>3247</v>
       </c>
       <c r="C28">
-        <v>2960</v>
+        <v>2954</v>
       </c>
       <c r="D28">
-        <v>1949</v>
+        <v>1942</v>
       </c>
       <c r="E28">
-        <v>2905</v>
+        <v>2900</v>
       </c>
       <c r="F28">
-        <v>2361</v>
+        <v>2341</v>
       </c>
       <c r="G28">
-        <v>2684.4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2676.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>34</v>
       </c>
       <c r="B29">
-        <v>4270</v>
+        <v>4269</v>
       </c>
       <c r="C29">
-        <v>3493</v>
+        <v>3486</v>
       </c>
       <c r="D29">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="E29">
-        <v>3469</v>
+        <v>3472</v>
       </c>
       <c r="F29">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="G29">
-        <v>3306.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>3304.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>35</v>
       </c>
       <c r="B30">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="C30">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="D30">
         <v>1622</v>
       </c>
       <c r="E30">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F30">
         <v>378</v>
       </c>
       <c r="G30">
-        <v>1498</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1497.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -8840,30 +7325,30 @@
         <v>1632.2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>37</v>
       </c>
       <c r="B32">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="C32">
         <v>2864</v>
       </c>
       <c r="D32">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="E32">
         <v>461</v>
       </c>
       <c r="F32">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G32">
-        <v>1637.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1637.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -8886,7 +7371,7 @@
         <v>3190.6</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -8906,10 +7391,10 @@
         <v>24</v>
       </c>
       <c r="G34">
-        <v>33.200000000000003</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -8932,7 +7417,7 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -8955,30 +7440,30 @@
         <v>37.6</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C37">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D37">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E37">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F37">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G37">
-        <v>46.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -9001,12 +7486,12 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>44</v>
       </c>
       <c r="B39">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C39">
         <v>42</v>
@@ -9021,10 +7506,10 @@
         <v>18</v>
       </c>
       <c r="G39">
-        <v>29.4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -9047,7 +7532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -9070,76 +7555,76 @@
         <v>45.8</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C42">
         <v>44</v>
       </c>
       <c r="D42">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E42">
         <v>49</v>
       </c>
       <c r="F42">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G42">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C43">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D43">
         <v>61</v>
       </c>
       <c r="E43">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F43">
         <v>29</v>
       </c>
       <c r="G43">
-        <v>50.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>49</v>
       </c>
       <c r="B44">
-        <v>2604</v>
+        <v>2601</v>
       </c>
       <c r="C44">
-        <v>2107</v>
+        <v>2111</v>
       </c>
       <c r="D44">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="E44">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="F44">
         <v>245</v>
       </c>
       <c r="G44">
-        <v>1376.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1367.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -9162,30 +7647,30 @@
         <v>1526.6</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>51</v>
       </c>
       <c r="B46">
-        <v>2163</v>
+        <v>2167</v>
       </c>
       <c r="C46">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="D46">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="E46">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F46">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="G46">
-        <v>1540.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1541.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -9193,45 +7678,45 @@
         <v>3247</v>
       </c>
       <c r="C47">
-        <v>2960</v>
+        <v>2954</v>
       </c>
       <c r="D47">
-        <v>1949</v>
+        <v>1942</v>
       </c>
       <c r="E47">
-        <v>2905</v>
+        <v>2900</v>
       </c>
       <c r="F47">
-        <v>2361</v>
+        <v>2341</v>
       </c>
       <c r="G47">
-        <v>2684.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+        <v>2676.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>53</v>
       </c>
       <c r="B48">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="C48">
         <v>2864</v>
       </c>
       <c r="D48">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="E48">
         <v>461</v>
       </c>
       <c r="F48">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G48">
-        <v>1637.2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1637.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -9251,33 +7736,33 @@
         <v>24</v>
       </c>
       <c r="G49">
-        <v>33.200000000000003</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>55</v>
       </c>
       <c r="B50">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C50">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D50">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E50">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F50">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G50">
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -9300,7 +7785,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -9323,58 +7808,58 @@
         <v>32.6</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>58</v>
       </c>
       <c r="B53">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C53">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D53">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E53">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F53">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G53">
-        <v>43.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="B54">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C54">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="D54">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E54">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F54">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G54">
-        <v>46.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>60</v>
       </c>
       <c r="B55">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C55">
         <v>42</v>
@@ -9389,10 +7874,10 @@
         <v>18</v>
       </c>
       <c r="G55">
-        <v>29.4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -9415,7 +7900,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -9438,76 +7923,76 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="B58">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C58">
         <v>44</v>
       </c>
       <c r="D58">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E58">
         <v>49</v>
       </c>
       <c r="F58">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G58">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>64</v>
       </c>
       <c r="B59">
-        <v>2163</v>
+        <v>2167</v>
       </c>
       <c r="C59">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="D59">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="E59">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F59">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="G59">
-        <v>1540.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1541.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>65</v>
       </c>
       <c r="B60">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C60">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D60">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E60">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F60">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G60">
-        <v>36.6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -9530,53 +8015,53 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="B62">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C62">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D62">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E62">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F62">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G62">
-        <v>37.799999999999997</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>68</v>
       </c>
       <c r="B63">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C63">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="D63">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E63">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F63">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G63">
-        <v>43.8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -9599,27 +8084,27 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>70</v>
       </c>
       <c r="B65">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C65">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D65">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E65">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F65">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G65">
-        <v>37.799999999999997</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -9628,11 +8113,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9655,7 +8140,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -9678,7 +8163,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -9701,7 +8186,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -9724,7 +8209,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -9747,7 +8232,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -9770,7 +8255,7 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -9793,7 +8278,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -9816,7 +8301,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -9836,10 +8321,10 @@
         <v>12</v>
       </c>
       <c r="G9">
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -9862,7 +8347,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -9885,7 +8370,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -9908,7 +8393,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -9931,7 +8416,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -9954,7 +8439,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -9977,7 +8462,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -10000,7 +8485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -10023,7 +8508,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -10043,10 +8528,10 @@
         <v>4</v>
       </c>
       <c r="G18">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -10069,7 +8554,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -10092,7 +8577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -10115,12 +8600,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>11</v>
@@ -10135,10 +8620,10 @@
         <v>3</v>
       </c>
       <c r="G22">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -10161,7 +8646,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -10184,7 +8669,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -10198,16 +8683,16 @@
         <v>24</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F25">
         <v>12</v>
       </c>
       <c r="G25">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -10227,10 +8712,10 @@
         <v>12</v>
       </c>
       <c r="G26">
-        <v>16.399999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -10253,7 +8738,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -10273,10 +8758,10 @@
         <v>12</v>
       </c>
       <c r="G28">
-        <v>18.600000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -10290,16 +8775,16 @@
         <v>13</v>
       </c>
       <c r="E29">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F29">
         <v>2</v>
       </c>
       <c r="G29">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>35</v>
       </c>
@@ -10322,7 +8807,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>36</v>
       </c>
@@ -10345,7 +8830,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>37</v>
       </c>
@@ -10368,7 +8853,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>38</v>
       </c>
@@ -10391,7 +8876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -10414,7 +8899,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -10437,7 +8922,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -10460,30 +8945,30 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>42</v>
       </c>
       <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>12</v>
+      </c>
+      <c r="D37">
+        <v>14</v>
+      </c>
+      <c r="E37">
         <v>10</v>
-      </c>
-      <c r="C37">
-        <v>16</v>
-      </c>
-      <c r="D37">
-        <v>8</v>
-      </c>
-      <c r="E37">
-        <v>15</v>
       </c>
       <c r="F37">
         <v>4</v>
       </c>
       <c r="G37">
-        <v>10.6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>43</v>
       </c>
@@ -10503,10 +8988,10 @@
         <v>5</v>
       </c>
       <c r="G38">
-        <v>8.8000000000000007</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -10529,7 +9014,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -10552,7 +9037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -10572,15 +9057,15 @@
         <v>2</v>
       </c>
       <c r="G41">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>47</v>
       </c>
       <c r="B42">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>11</v>
@@ -10592,18 +9077,18 @@
         <v>13</v>
       </c>
       <c r="F42">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G42">
-        <v>11.2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>48</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>9</v>
@@ -10618,10 +9103,10 @@
         <v>2</v>
       </c>
       <c r="G43">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -10641,10 +9126,10 @@
         <v>4</v>
       </c>
       <c r="G44">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -10664,10 +9149,10 @@
         <v>5</v>
       </c>
       <c r="G45">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -10690,7 +9175,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -10713,7 +9198,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -10736,7 +9221,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -10756,10 +9241,10 @@
         <v>4</v>
       </c>
       <c r="G49">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -10770,19 +9255,19 @@
         <v>14</v>
       </c>
       <c r="D50">
+        <v>14</v>
+      </c>
+      <c r="E50">
         <v>12</v>
       </c>
-      <c r="E50">
-        <v>11</v>
-      </c>
       <c r="F50">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G50">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>56</v>
       </c>
@@ -10805,7 +9290,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>57</v>
       </c>
@@ -10828,7 +9313,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>58</v>
       </c>
@@ -10836,45 +9321,45 @@
         <v>10</v>
       </c>
       <c r="C53">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D53">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E53">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G53">
-        <v>10.6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>59</v>
       </c>
       <c r="B54">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D54">
+        <v>13</v>
+      </c>
+      <c r="E54">
         <v>7</v>
-      </c>
-      <c r="E54">
-        <v>11</v>
       </c>
       <c r="F54">
         <v>2</v>
       </c>
       <c r="G54">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>60</v>
       </c>
@@ -10894,10 +9379,10 @@
         <v>5</v>
       </c>
       <c r="G55">
-        <v>8.8000000000000007</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>61</v>
       </c>
@@ -10920,7 +9405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>62</v>
       </c>
@@ -10943,12 +9428,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>63</v>
       </c>
       <c r="B58">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C58">
         <v>9</v>
@@ -10960,13 +9445,13 @@
         <v>9</v>
       </c>
       <c r="F58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -10986,33 +9471,33 @@
         <v>5</v>
       </c>
       <c r="G59">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>65</v>
       </c>
       <c r="B60">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D60">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E60">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G60">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -11035,30 +9520,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>67</v>
       </c>
       <c r="B62">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C62">
         <v>14</v>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E62">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G62">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>68</v>
       </c>
@@ -11069,19 +9554,19 @@
         <v>11</v>
       </c>
       <c r="D63">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E63">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G63">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -11104,27 +9589,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>70</v>
       </c>
       <c r="B65">
+        <v>10</v>
+      </c>
+      <c r="C65">
         <v>11</v>
       </c>
-      <c r="C65">
+      <c r="D65">
+        <v>14</v>
+      </c>
+      <c r="E65">
         <v>10</v>
       </c>
-      <c r="D65">
-        <v>11</v>
-      </c>
-      <c r="E65">
-        <v>7</v>
-      </c>
       <c r="F65">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G65">
-        <v>9.4</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
